--- a/02_景锐培训作业/08_激励与引导-实践作业-周静.xlsx
+++ b/02_景锐培训作业/08_激励与引导-实践作业-周静.xlsx
@@ -353,7 +353,7 @@
     <t>三十天内完成一对一谈心，多倾听诉求，少单向下达指令。（15学分）</t>
   </si>
   <si>
-    <t>已基于2026年8月5日的人员沟通完成第一轮谈心记录。沟通方式不是先下任务，而是按“上半年工作—下半年计划—当前诉求”三步倾听，让成员先表达真实状态。
+    <t>已基于近期的人员沟通完成第一轮谈心记录。沟通方式不是先下任务，而是按“上半年工作—下半年计划—当前诉求”三步倾听，让成员先表达真实状态。
 关键反馈：
 - 员工B：平台方向上半年完成一体化协议平台、DPDK/1Gbps、全定向项目支撑；下半年要做平台收尾、认证/虚拟网桥CBB、自研网桥和VPP数据处理框架。反馈的核心困难是没有设备。后续动作：设备诉求纳入风险台账，明确没有设备会影响哪些验证节点。
 - 员工C：承担1253、1227、51392、1315等多项目支撑，还要带新员工。反馈协议平台多次更改、不适配其他项目、出现问题需要个人排查，同时对1320V2.0不熟，人力紧。后续动作：全向主线由其牵住，但不把所有项目救火都压给个人；新人从文档、小需求、问题复盘切入分担低风险工作。
